--- a/artfynd/A 58596-2022 artfynd.xlsx
+++ b/artfynd/A 58596-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58596-2022 artfynd.xlsx
+++ b/artfynd/A 58596-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3054,10 +3054,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>103957255</v>
+        <v>103957353</v>
       </c>
       <c r="B23" t="n">
-        <v>78569</v>
+        <v>78602</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3066,25 +3066,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3094,10 +3094,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>658038.2459494971</v>
+        <v>658024.6108731303</v>
       </c>
       <c r="R23" t="n">
-        <v>7192172.517143697</v>
+        <v>7192147.476244624</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3166,10 +3166,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>103957353</v>
+        <v>103956302</v>
       </c>
       <c r="B24" t="n">
-        <v>78602</v>
+        <v>88476</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3178,38 +3178,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>1962</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Slänttjärnen, Ly lm</t>
+          <t>Slänttjärnen, Mettjaur, Lycksele, Ly lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>658024.6108731303</v>
+        <v>657958.8382558227</v>
       </c>
       <c r="R24" t="n">
-        <v>7192147.476244624</v>
+        <v>7192114.57044916</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3266,22 +3266,26 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>103956302</v>
+        <v>103957209</v>
       </c>
       <c r="B25" t="n">
-        <v>88476</v>
+        <v>78570</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3294,34 +3298,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1962</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Slänttjärnen, Mettjaur, Lycksele, Ly lm</t>
+          <t>Slänttjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>657958.8382558227</v>
+        <v>658004.8991135582</v>
       </c>
       <c r="R25" t="n">
-        <v>7192114.57044916</v>
+        <v>7192132.356735424</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3378,131 +3382,15 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>103957209</v>
-      </c>
-      <c r="B26" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Slänttjärnen, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>658004.8991135582</v>
-      </c>
-      <c r="R26" t="n">
-        <v>7192132.356735424</v>
-      </c>
-      <c r="S26" t="n">
-        <v>10</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58596-2022 artfynd.xlsx
+++ b/artfynd/A 58596-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>86421600</v>
+        <v>103957266</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Falträsk, Ly lm</t>
+          <t>Slänttjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>658037.8422961918</v>
+        <v>658038</v>
       </c>
       <c r="R2" t="n">
-        <v>7192172.069172813</v>
+        <v>7192171</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs inventering.</t>
+          <t>2022-10-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>86421601</v>
+        <v>103956302</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,41 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1962</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Falträsk, Ly lm</t>
+          <t>Slänttjärnen, Mettjaur, Lycksele, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>658006.0429035885</v>
+        <v>657959</v>
       </c>
       <c r="R3" t="n">
-        <v>7192134.97728282</v>
+        <v>7192115</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,27 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs inventering.</t>
+          <t>2022-10-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,27 +857,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103957189</v>
+        <v>103957249</v>
       </c>
       <c r="B4" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,39 +884,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Slänttjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>658023.803144212</v>
+        <v>657892</v>
       </c>
       <c r="R4" t="n">
-        <v>7192138.472553286</v>
+        <v>7192171</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,19 +941,9 @@
           <t>2022-10-06</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,15 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103957281</v>
+        <v>103957207</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1050,21 +981,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1074,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>658017.3652345845</v>
+        <v>658038</v>
       </c>
       <c r="R5" t="n">
-        <v>7192098.448150232</v>
+        <v>7192171</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,19 +1038,9 @@
           <t>2022-10-06</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,37 +1067,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103957114</v>
+        <v>103957209</v>
       </c>
       <c r="B6" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1186,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>658030.080479202</v>
+        <v>658005</v>
       </c>
       <c r="R6" t="n">
-        <v>7192108.505545619</v>
+        <v>7192132</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,19 +1135,9 @@
           <t>2022-10-06</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,50 +1164,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103957352</v>
+        <v>103956303</v>
       </c>
       <c r="B7" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Slänttjärnen, Ly lm</t>
+          <t>Slänttjärnen, Mettjaur, Lycksele, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>658034.4330736339</v>
+        <v>657934</v>
       </c>
       <c r="R7" t="n">
-        <v>7192155.674335738</v>
+        <v>7192147</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,19 +1232,9 @@
           <t>2022-10-06</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,49 +1249,48 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103957271</v>
+        <v>103957114</v>
       </c>
       <c r="B8" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1410,10 +1300,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>658006.5590262904</v>
+        <v>658030</v>
       </c>
       <c r="R8" t="n">
-        <v>7192141.405291231</v>
+        <v>7192109</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1443,19 +1333,9 @@
           <t>2022-10-06</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,37 +1362,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103957257</v>
+        <v>103957115</v>
       </c>
       <c r="B9" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1522,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>658007.5674973874</v>
+        <v>658026</v>
       </c>
       <c r="R9" t="n">
-        <v>7192130.363577899</v>
+        <v>7192124</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,19 +1430,9 @@
           <t>2022-10-06</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,37 +1459,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103957188</v>
+        <v>103957281</v>
       </c>
       <c r="B10" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1634,10 +1494,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>658024.4540535072</v>
+        <v>658017</v>
       </c>
       <c r="R10" t="n">
-        <v>7192150.455039054</v>
+        <v>7192099</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1667,19 +1527,9 @@
           <t>2022-10-06</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,37 +1556,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103957211</v>
+        <v>103957282</v>
       </c>
       <c r="B11" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1746,10 +1591,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>658038.290759076</v>
+        <v>658072</v>
       </c>
       <c r="R11" t="n">
-        <v>7192171.66606607</v>
+        <v>7192203</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1779,19 +1624,9 @@
           <t>2022-10-06</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,37 +1653,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103957355</v>
+        <v>103957271</v>
       </c>
       <c r="B12" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1858,10 +1688,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>658004.8095136113</v>
+        <v>658006</v>
       </c>
       <c r="R12" t="n">
-        <v>7192134.058912456</v>
+        <v>7192141</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1891,19 +1721,9 @@
           <t>2022-10-06</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1930,37 +1750,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103957282</v>
+        <v>103957211</v>
       </c>
       <c r="B13" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1970,10 +1785,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>658071.6812524635</v>
+        <v>658038</v>
       </c>
       <c r="R13" t="n">
-        <v>7192202.867729237</v>
+        <v>7192172</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2003,19 +1818,9 @@
           <t>2022-10-06</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2042,53 +1847,52 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103957266</v>
+        <v>86421600</v>
       </c>
       <c r="B14" t="n">
-        <v>73680</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>306</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Slänttjärnen, Ly lm</t>
+          <t>Falträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>658038.3355686651</v>
+        <v>658038</v>
       </c>
       <c r="R14" t="n">
-        <v>7192170.814988202</v>
+        <v>7192172</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2112,22 +1916,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs inventering.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2142,65 +1941,64 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103957261</v>
+        <v>86421601</v>
       </c>
       <c r="B15" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Slänttjärnen, Ly lm</t>
+          <t>Falträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>658004.6970493145</v>
+        <v>658006</v>
       </c>
       <c r="R15" t="n">
-        <v>7192128.078861297</v>
+        <v>7192135</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2224,22 +2022,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-11</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs inventering.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2254,62 +2047,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>103956303</v>
+        <v>103957256</v>
       </c>
       <c r="B16" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Slänttjärnen, Mettjaur, Lycksele, Ly lm</t>
+          <t>Slänttjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>657933.6134144575</v>
+        <v>658022</v>
       </c>
       <c r="R16" t="n">
-        <v>7192147.380962761</v>
+        <v>7192145</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2339,19 +2127,9 @@
           <t>2022-10-06</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2366,31 +2144,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>103957256</v>
+        <v>103957257</v>
       </c>
       <c r="B17" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2422,10 +2191,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>658022.5701753353</v>
+        <v>658008</v>
       </c>
       <c r="R17" t="n">
-        <v>7192145.661925008</v>
+        <v>7192130</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2455,19 +2224,9 @@
           <t>2022-10-06</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2494,15 +2253,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>103957115</v>
+        <v>103957186</v>
       </c>
       <c r="B18" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2510,21 +2264,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2534,10 +2288,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>658025.8206285734</v>
+        <v>658053</v>
       </c>
       <c r="R18" t="n">
-        <v>7192124.49687409</v>
+        <v>7192153</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2567,19 +2321,9 @@
           <t>2022-10-06</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2606,15 +2350,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>103957260</v>
+        <v>103957187</v>
       </c>
       <c r="B19" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2622,21 +2361,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2646,10 +2385,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>658032.5720041711</v>
+        <v>658038</v>
       </c>
       <c r="R19" t="n">
-        <v>7192158.563396484</v>
+        <v>7192172</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2679,19 +2418,9 @@
           <t>2022-10-06</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2718,37 +2447,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>103957207</v>
+        <v>103957188</v>
       </c>
       <c r="B20" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2758,10 +2482,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>658038.3355686651</v>
+        <v>658025</v>
       </c>
       <c r="R20" t="n">
-        <v>7192170.814988202</v>
+        <v>7192150</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2791,19 +2515,9 @@
           <t>2022-10-06</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2830,15 +2544,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>103957186</v>
+        <v>103957352</v>
       </c>
       <c r="B21" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2846,21 +2555,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2870,10 +2579,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>658052.5292698664</v>
+        <v>658034</v>
       </c>
       <c r="R21" t="n">
-        <v>7192152.786642901</v>
+        <v>7192156</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2903,19 +2612,9 @@
           <t>2022-10-06</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2942,15 +2641,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>103957187</v>
+        <v>103957353</v>
       </c>
       <c r="B22" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2958,21 +2652,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2982,10 +2676,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>658038.290759076</v>
+        <v>658024</v>
       </c>
       <c r="R22" t="n">
-        <v>7192171.66606607</v>
+        <v>7192147</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3015,19 +2709,9 @@
           <t>2022-10-06</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3054,15 +2738,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>103957353</v>
+        <v>103957355</v>
       </c>
       <c r="B23" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3094,10 +2773,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>658024.6108731303</v>
+        <v>658005</v>
       </c>
       <c r="R23" t="n">
-        <v>7192147.476244624</v>
+        <v>7192134</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3127,19 +2806,9 @@
           <t>2022-10-06</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3166,50 +2835,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>103956302</v>
+        <v>103957260</v>
       </c>
       <c r="B24" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1962</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Slänttjärnen, Mettjaur, Lycksele, Ly lm</t>
+          <t>Slänttjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>657958.8382558227</v>
+        <v>658032</v>
       </c>
       <c r="R24" t="n">
-        <v>7192114.57044916</v>
+        <v>7192158</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3239,19 +2903,9 @@
           <t>2022-10-06</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3266,53 +2920,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>103957209</v>
+        <v>103957261</v>
       </c>
       <c r="B25" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3322,10 +2967,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>658004.8991135582</v>
+        <v>658005</v>
       </c>
       <c r="R25" t="n">
-        <v>7192132.356735424</v>
+        <v>7192128</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3355,19 +3000,9 @@
           <t>2022-10-06</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3391,6 +3026,108 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>103957189</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Slänttjärnen, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>658024</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7192138</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2022-10-06</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2022-10-06</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58596-2022 artfynd.xlsx
+++ b/artfynd/A 58596-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103957266</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103956302</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103957249</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103957207</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103957209</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1262,6 +1292,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103956303</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1359,6 +1394,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103957114</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1456,6 +1496,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103957115</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1553,6 +1598,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103957281</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1650,6 +1700,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103957282</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1747,6 +1802,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103957271</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1844,6 +1904,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103957211</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1950,6 +2015,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86421600</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2056,6 +2126,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86421601</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2153,6 +2228,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103957256</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2250,6 +2330,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103957257</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2347,6 +2432,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103957186</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2444,6 +2534,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103957187</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2541,6 +2636,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103957188</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2638,6 +2738,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103957352</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2735,6 +2840,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103957353</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2832,6 +2942,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103957355</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2929,6 +3044,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103957260</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3026,6 +3146,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103957261</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3128,8 +3253,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103957189</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>